--- a/heavy_meteorites.xlsx
+++ b/heavy_meteorites.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,15 +463,15 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Queen Alexandra Range 93148</t>
+          <t>Allan Hills 84001</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>84000</v>
+        <v>1930</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Pallasite</t>
+          <t>Martian</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -485,35 +485,455 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1993</v>
+        <v>1984</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>Hoba</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>60000000</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Iron</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Found</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Africa</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>1920</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Campo del Cielo</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>50000000</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Iron</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Found</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>South America</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>1576</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Tagish Lake</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>10000</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Carbonaceous Chondrite</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Fell</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>North America</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Chelyabinsk</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ordinary Chondrite</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Fell</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Russia</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>2013</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Sikhote-Alin</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>23000000</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Iron</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Fell</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Russia</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>1947</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Nantan</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>9500000</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Iron</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Found</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>1516</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Yamato 000593</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>13700</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Martian</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Found</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Antarctica</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Elephant Moraine 79001</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>7900</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Martian</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Found</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Antarctica</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>1979</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Sahara 97096</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>26500</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Enstatite Chondrite</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Found</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Sahara</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>1997</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Acfer 059</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>200</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Chondrite</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Found</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Sahara</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>1989</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Gibeon</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>26000000</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Iron</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Found</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Africa</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>1836</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Canyon Diablo</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>30000000</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Iron</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Found</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>North America</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>1891</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Peekskill</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>12400</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ordinary Chondrite</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Fell</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>North America</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>1992</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Queen Alexandra Range 93148</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>84000</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Pallasite</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Found</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Antarctica</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>1993</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>Gao-Guenie</t>
         </is>
       </c>
-      <c r="B3" t="n">
+      <c r="B17" t="n">
         <v>100000</v>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>Ordinary Chondrite</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>Fell</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>Sahara</t>
         </is>
       </c>
-      <c r="F3" t="n">
+      <c r="F17" t="n">
         <v>1960</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Murchison</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>100000</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Carbonaceous Chondrite</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Fell</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>1969</v>
       </c>
     </row>
   </sheetData>
